--- a/docs/05-Power-Budget/10-29-25_PB.xlsx
+++ b/docs/05-Power-Budget/10-29-25_PB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2004l\OneDrive - Arizona State University\Desktop\ASUDrive\OneDrive - Arizona State University\Documents\EGR 304\lryan5.github.io\docs\05-Power-Budget\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58C29D9-E85C-4EF8-8374-585005ACF73D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AEC3252-3F51-4549-AECB-FA9C1CA7BBD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1662,6 +1662,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/docs/05-Power-Budget/10-29-25_PB.xlsx
+++ b/docs/05-Power-Budget/10-29-25_PB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2004l\OneDrive - Arizona State University\Desktop\ASUDrive\OneDrive - Arizona State University\Documents\EGR 304\lryan5.github.io\docs\05-Power-Budget\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AEC3252-3F51-4549-AECB-FA9C1CA7BBD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA82BDD-E3F4-44D3-AAA1-43EAAC47A807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Power Budget" sheetId="1" r:id="rId1"/>
@@ -289,7 +289,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -464,11 +464,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -548,40 +581,51 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -947,16 +991,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1001,7 +1045,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="3"/>
@@ -1021,16 +1065,16 @@
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="41"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="44"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
@@ -1051,7 +1095,7 @@
       <c r="F8" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="51" t="s">
+      <c r="G8" s="37" t="s">
         <v>11</v>
       </c>
       <c r="H8" s="11" t="s">
@@ -1185,16 +1229,16 @@
       <c r="H15" s="21"/>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="39" t="s">
+      <c r="A16" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="40"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="41"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="44"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="22" t="s">
@@ -1336,13 +1380,13 @@
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="12"/>
-      <c r="B23" s="42" t="s">
+      <c r="B23" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48"/>
       <c r="G23" s="15">
         <f>SUM(G18:G22)</f>
         <v>570</v>
@@ -1353,13 +1397,13 @@
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="12"/>
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="38"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
       <c r="G24" s="23">
         <v>0.25</v>
       </c>
@@ -1367,13 +1411,13 @@
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="24"/>
-      <c r="B25" s="43" t="s">
+      <c r="B25" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="38"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
       <c r="G25" s="15">
         <f>G23*(1+G24)</f>
         <v>712.5</v>
@@ -1421,13 +1465,13 @@
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="29"/>
-      <c r="B28" s="44" t="s">
+      <c r="B28" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
       <c r="G28" s="28">
         <f>G27-G25</f>
         <v>287.5</v>
@@ -1437,38 +1481,38 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="39" t="s">
+      <c r="A29" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="40"/>
-      <c r="C29" s="40"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="40"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="41"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="44"/>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="47"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="48"/>
+      <c r="A30" s="39"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="41"/>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="39" t="s">
+      <c r="A31" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="40"/>
-      <c r="C31" s="40"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="41"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="44"/>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="22" t="s">
@@ -1533,7 +1577,7 @@
       <c r="H34" s="36"/>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="49" t="s">
+      <c r="A35" s="45" t="s">
         <v>32</v>
       </c>
       <c r="B35" s="26" t="s">
@@ -1559,14 +1603,14 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="50"/>
-      <c r="B36" s="46" t="s">
+      <c r="A36" s="46"/>
+      <c r="B36" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
       <c r="G36" s="33">
         <f>G33-SUM(G35:G35)</f>
         <v>13500</v>
@@ -1576,25 +1620,75 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="50"/>
+      <c r="A37" s="46"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="20"/>
       <c r="E37" s="20"/>
-      <c r="F37" s="52"/>
-      <c r="G37" s="52"/>
-      <c r="H37" s="52"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="56"/>
+      <c r="H37" s="57"/>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="35"/>
+      <c r="A38" s="54"/>
+      <c r="B38" s="55"/>
+      <c r="C38" s="55"/>
+      <c r="D38" s="55"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="55"/>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="35"/>
-    </row>
-    <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+      <c r="A39" s="38"/>
+      <c r="B39" s="53"/>
+      <c r="C39" s="53"/>
+      <c r="D39" s="53"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="53"/>
+      <c r="G39" s="53"/>
+      <c r="H39" s="53"/>
+    </row>
+    <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="53"/>
+      <c r="B40" s="53"/>
+      <c r="C40" s="53"/>
+      <c r="D40" s="53"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="53"/>
+      <c r="G40" s="53"/>
+      <c r="H40" s="53"/>
+    </row>
+    <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="53"/>
+      <c r="B41" s="53"/>
+      <c r="C41" s="53"/>
+      <c r="D41" s="53"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="53"/>
+      <c r="G41" s="53"/>
+      <c r="H41" s="53"/>
+    </row>
+    <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="53"/>
+      <c r="B42" s="53"/>
+      <c r="C42" s="53"/>
+      <c r="D42" s="53"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="53"/>
+      <c r="G42" s="53"/>
+      <c r="H42" s="53"/>
+    </row>
+    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="53"/>
+      <c r="B43" s="53"/>
+      <c r="C43" s="53"/>
+      <c r="D43" s="53"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="53"/>
+      <c r="G43" s="53"/>
+      <c r="H43" s="53"/>
+    </row>
     <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -1643,11 +1737,6 @@
     <row r="89" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="A29:H29"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="B24:F24"/>
@@ -1655,6 +1744,11 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="A29:H29"/>
   </mergeCells>
   <conditionalFormatting sqref="G28">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
